--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -5905,6 +5905,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5916,7 +6024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F168"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -11303,6 +11411,166 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>중진공, '재도전 힐링캠프' 참가자 모집…재창업자 심리회복 지원</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mt.co.kr/future/2026/09/13/2026091310023649634</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>중진공 재도전응원본부, ‘재도전 힐링캠프 ’ 참가자 모집</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dt.co.kr/article/12083591?ref=jeadan</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>중진공, '재도전 힐링캠프' 참여자 모집</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>https://view.asiae.co.kr/article/2026091311434327871</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>중진공, 재도전 나선 재창업자 지원한다</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>http://www.metroseoul.co.kr/article/20260912500045</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>‘장애 고백’ 이지아, 오랜만에 근황 공개…“더 예뻐졌다”</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sportsseoul.com/news/read/1634622</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G205"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -6013,6 +6013,114 @@
         <v>5</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6024,7 +6132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:F175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -11571,6 +11679,70 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>동두천시, 다문화가족 대상 ‘숲속 가족 힐링캠프’ 개최</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>https://www.munhwa.com/article/11616735?ref=kpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>가을바람 맞으며 즐긴 가족 캠핑…'2026 꿀잼대전 힐링캠프' 성료</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>https://www.joongdo.co.kr/web/view.php?key=20260913010004052</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_report.xlsx
+++ b/news_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.5" customWidth="1" min="1" max="1"/>
@@ -6121,6 +6121,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>노동분과위원회</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D213" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6132,7 +6240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F175"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.4" customWidth="1" min="1" max="1"/>
@@ -11743,6 +11851,422 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>광주 일자리재단, 소규모사업장 노동환경 개선 나서</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jnilbo.com/news/articleView.html?idxno=90000065698</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>광주경제진흥일자리재단, 소규모사업장 현장 목소리 청취</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>http://www.gwangnam.co.kr/article.php?aid=1789433117547045015</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>공연무대 설치 40대 외국인, 감전 심정지…동료 도움으로 회복</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Society/article/all/20260915/134669535/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>외국인노동자</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>‘ACLE 출격’ 베이징 원정 앞둔 포항 박태하 감독 “좋은 기억 많아”</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>https://www.donga.com/news/Sports/article/all/20260915/134668679/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>충남도 자경위, 제3차 숲 힐링캠프 운영</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ccdailynews.com/news/articleView.html?idxno=2440951</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>중진공, 재창업자 심리회복 ‘힐링캠프’ 운영</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>https://news.kbs.co.kr/news/view.do?ncd=8663554&amp;amp;ref=DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>[꿀잼대전 힐링캠프] "종이비행기 1등은 나"…2년 연속 수상한 재현군</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>https://www.joongdo.co.kr/web/view.php?key=20260914010004147</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>[꿀잼대전 힐링캠프] "가족과 함께 대전의 새로운 매력 느끼길"</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>https://www.joongdo.co.kr/web/view.php?key=20260914010004154</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>[꿀잼대전 힐링캠프 현장] 텐트 치고 불멍하며 도란도란…가족愛 피어난 상소동의 밤</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>https://www.joongdo.co.kr/web/view.php?key=20260913010004153</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>[꿀잼대전 힐링캠프] "무반주 휘파람에 무표정 춤"…무대 휘어잡은 형제</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>https://www.joongdo.co.kr/web/view.php?key=20260913010004150</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>[꿀잼대전 힐링캠프] "모든 프로그램 빠짐없이 즐겼어요"</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>https://www.joongdo.co.kr/web/view.php?key=20260914010004151</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>[꿀잼대전 힐링캠프] "아이들과 첫 캠핑, 요리대회 우승까지 했어요"</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>https://www.joongdo.co.kr/web/view.php?key=20260914010004148</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>빅카인즈 (BigKinds)</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>힐링캠프</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>중진공, 재창업자 지원 재도전 힐링캠프 운영</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kwnews.co.kr/article/20260914501502</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
